--- a/papers.xlsx
+++ b/papers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Documents\GitHub\ml-knowledge-inject-va\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C20B5D1-EF4F-4411-A47E-A8403473BC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE0A76C-BADB-4D32-8E59-84BC13B0DBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="426">
   <si>
     <t>Paper ID</t>
   </si>
@@ -1269,6 +1269,96 @@
   </si>
   <si>
     <t>10.1109/TVCG.2022.3141040</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2598838</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2598831</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2598830</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2598829</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2598828</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2745085</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2745258</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744805</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2745178</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2745158</t>
+  </si>
+  <si>
+    <t>10.1109/VAST.2017.8585720</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744378</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744683</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744158</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2746018</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2016.2618797</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2745859</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744320</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744358</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744718</t>
+  </si>
+  <si>
+    <t>10.1109/VAST.2017.8585721</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2744938</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864526</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2017.2764459</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864885</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864475</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864886</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864769</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865044</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864499</t>
   </si>
 </sst>
 </file>
@@ -9207,7 +9297,9 @@
       <c r="E224" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="F224" s="6"/>
+      <c r="F224" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
@@ -9240,7 +9332,9 @@
       <c r="E225" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="F225" s="6"/>
+      <c r="F225" s="6" t="s">
+        <v>425</v>
+      </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
@@ -9273,7 +9367,9 @@
       <c r="E226" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="F226" s="6"/>
+      <c r="F226" s="6" t="s">
+        <v>423</v>
+      </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
@@ -9341,7 +9437,9 @@
       <c r="E228" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F228" s="6"/>
+      <c r="F228" s="6" t="s">
+        <v>422</v>
+      </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
@@ -9374,7 +9472,9 @@
       <c r="E229" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F229" s="6"/>
+      <c r="F229" s="6" t="s">
+        <v>421</v>
+      </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
@@ -9407,7 +9507,9 @@
       <c r="E230" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F230" s="6"/>
+      <c r="F230" s="6" t="s">
+        <v>420</v>
+      </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
@@ -9440,7 +9542,9 @@
       <c r="E231" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F231" s="6"/>
+      <c r="F231" s="6" t="s">
+        <v>419</v>
+      </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
@@ -9473,7 +9577,9 @@
       <c r="E232" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F232" s="6"/>
+      <c r="F232" s="6" t="s">
+        <v>418</v>
+      </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
@@ -9541,7 +9647,9 @@
       <c r="E234" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F234" s="6"/>
+      <c r="F234" s="6" t="s">
+        <v>417</v>
+      </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
@@ -9574,7 +9682,9 @@
       <c r="E235" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F235" s="6"/>
+      <c r="F235" s="6" t="s">
+        <v>416</v>
+      </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
@@ -9607,7 +9717,9 @@
       <c r="E236" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F236" s="6"/>
+      <c r="F236" s="6" t="s">
+        <v>415</v>
+      </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
@@ -9640,7 +9752,9 @@
       <c r="E237" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F237" s="6"/>
+      <c r="F237" s="6" t="s">
+        <v>414</v>
+      </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
@@ -9673,7 +9787,9 @@
       <c r="E238" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F238" s="6"/>
+      <c r="F238" s="6" t="s">
+        <v>413</v>
+      </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
@@ -9706,7 +9822,9 @@
       <c r="E239" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F239" s="6"/>
+      <c r="F239" s="6" t="s">
+        <v>412</v>
+      </c>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
@@ -9739,7 +9857,9 @@
       <c r="E240" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F240" s="6"/>
+      <c r="F240" s="6" t="s">
+        <v>411</v>
+      </c>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
@@ -9772,7 +9892,9 @@
       <c r="E241" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F241" s="6"/>
+      <c r="F241" s="6" t="s">
+        <v>410</v>
+      </c>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
@@ -9805,7 +9927,9 @@
       <c r="E242" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F242" s="6"/>
+      <c r="F242" s="6" t="s">
+        <v>409</v>
+      </c>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
@@ -9838,7 +9962,9 @@
       <c r="E243" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F243" s="6"/>
+      <c r="F243" s="6" t="s">
+        <v>408</v>
+      </c>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
@@ -9871,7 +9997,9 @@
       <c r="E244" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F244" s="6"/>
+      <c r="F244" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
@@ -9904,7 +10032,9 @@
       <c r="E245" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F245" s="6"/>
+      <c r="F245" s="6" t="s">
+        <v>406</v>
+      </c>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
@@ -9937,7 +10067,9 @@
       <c r="E246" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F246" s="6"/>
+      <c r="F246" s="6" t="s">
+        <v>405</v>
+      </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
@@ -9970,7 +10102,9 @@
       <c r="E247" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F247" s="6"/>
+      <c r="F247" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
@@ -10003,7 +10137,9 @@
       <c r="E248" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F248" s="6"/>
+      <c r="F248" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
@@ -10036,7 +10172,9 @@
       <c r="E249" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F249" s="6"/>
+      <c r="F249" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
@@ -10069,7 +10207,9 @@
       <c r="E250" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F250" s="6"/>
+      <c r="F250" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
@@ -10102,7 +10242,9 @@
       <c r="E251" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F251" s="6"/>
+      <c r="F251" s="6" t="s">
+        <v>400</v>
+      </c>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
@@ -10135,7 +10277,9 @@
       <c r="E252" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F252" s="6"/>
+      <c r="F252" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
@@ -10168,7 +10312,9 @@
       <c r="E253" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F253" s="6"/>
+      <c r="F253" s="6" t="s">
+        <v>398</v>
+      </c>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
@@ -10201,7 +10347,9 @@
       <c r="E254" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F254" s="6"/>
+      <c r="F254" s="6" t="s">
+        <v>397</v>
+      </c>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="2"/>
@@ -10234,7 +10382,9 @@
       <c r="E255" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F255" s="6"/>
+      <c r="F255" s="6" t="s">
+        <v>396</v>
+      </c>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="2"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Documents\GitHub\ml-knowledge-inject-va\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE0A76C-BADB-4D32-8E59-84BC13B0DBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647CD1EB-4408-40C1-9BBC-B3E5E98B8FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="433">
   <si>
     <t>Paper ID</t>
   </si>
@@ -1359,6 +1359,27 @@
   </si>
   <si>
     <t>10.1109/TVCG.2018.2864499</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865027</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864504</t>
+  </si>
+  <si>
+    <t>10.1109/VAST.2018.8802509</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2843369</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2864903</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865145</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865119</t>
   </si>
 </sst>
 </file>
@@ -8827,7 +8848,9 @@
       <c r="E210" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F210" s="6"/>
+      <c r="F210" s="6" t="s">
+        <v>432</v>
+      </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
@@ -8860,7 +8883,9 @@
       <c r="E211" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F211" s="6"/>
+      <c r="F211" s="6" t="s">
+        <v>431</v>
+      </c>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
@@ -8893,7 +8918,9 @@
       <c r="E212" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F212" s="6"/>
+      <c r="F212" s="6" t="s">
+        <v>430</v>
+      </c>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -9095,7 +9122,9 @@
       <c r="E218" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F218" s="6"/>
+      <c r="F218" s="6" t="s">
+        <v>429</v>
+      </c>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
@@ -9128,7 +9157,9 @@
       <c r="E219" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F219" s="6"/>
+      <c r="F219" s="6" t="s">
+        <v>428</v>
+      </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -9161,7 +9192,9 @@
       <c r="E220" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F220" s="6"/>
+      <c r="F220" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
@@ -9194,7 +9227,9 @@
       <c r="E221" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F221" s="6"/>
+      <c r="F221" s="6" t="s">
+        <v>426</v>
+      </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Documents\GitHub\ml-knowledge-inject-va\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647CD1EB-4408-40C1-9BBC-B3E5E98B8FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A0C3C-33BC-4E93-AC8D-893AAF2554E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="468">
   <si>
     <t>Paper ID</t>
   </si>
@@ -1380,6 +1380,111 @@
   </si>
   <si>
     <t>10.1109/TVCG.2018.2865119</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209361</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209347</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209425</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3182488</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3099002</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3167896</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3106142</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3148745</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209419</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209468</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3146806</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209413</t>
+  </si>
+  <si>
+    <t>10.48550/arXiv.2204.01888</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3184186</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3184247</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3152450</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3097709</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3209479</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2022.3169590</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3114784</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3114837</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3114793</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3114794</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3114858</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2021.3076749</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028958</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030471</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030455</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2024.3456142</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.2978050</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030430</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030383</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.2995100</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2961674</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028894</t>
   </si>
 </sst>
 </file>
@@ -3464,7 +3569,9 @@
       <c r="E50" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>461</v>
+      </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -5598,7 +5705,9 @@
       <c r="E112" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F112" s="4"/>
+      <c r="F112" s="4" t="s">
+        <v>433</v>
+      </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -5631,7 +5740,9 @@
       <c r="E113" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F113" s="4"/>
+      <c r="F113" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
@@ -5664,7 +5775,9 @@
       <c r="E114" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F114" s="4"/>
+      <c r="F114" s="4" t="s">
+        <v>435</v>
+      </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
@@ -5697,7 +5810,9 @@
       <c r="E115" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F115" s="4"/>
+      <c r="F115" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
@@ -5730,7 +5845,9 @@
       <c r="E116" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F116" s="4"/>
+      <c r="F116" s="4" t="s">
+        <v>437</v>
+      </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -5763,7 +5880,9 @@
       <c r="E117" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F117" s="4"/>
+      <c r="F117" s="4" t="s">
+        <v>438</v>
+      </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -5796,7 +5915,9 @@
       <c r="E118" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F118" s="4"/>
+      <c r="F118" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
@@ -5829,7 +5950,9 @@
       <c r="E119" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F119" s="4"/>
+      <c r="F119" s="4" t="s">
+        <v>440</v>
+      </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -5862,7 +5985,9 @@
       <c r="E120" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F120" s="4"/>
+      <c r="F120" s="4" t="s">
+        <v>441</v>
+      </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
@@ -5895,7 +6020,9 @@
       <c r="E121" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F121" s="4"/>
+      <c r="F121" s="4" t="s">
+        <v>442</v>
+      </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
@@ -6126,7 +6253,9 @@
       <c r="E128" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F128" s="4"/>
+      <c r="F128" s="4" t="s">
+        <v>443</v>
+      </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
@@ -6159,7 +6288,9 @@
       <c r="E129" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F129" s="4"/>
+      <c r="F129" s="4" t="s">
+        <v>444</v>
+      </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
@@ -6192,7 +6323,9 @@
       <c r="E130" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F130" s="4"/>
+      <c r="F130" s="4" t="s">
+        <v>445</v>
+      </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
@@ -6330,7 +6463,9 @@
       <c r="E134" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F134" s="4"/>
+      <c r="F134" s="4" t="s">
+        <v>446</v>
+      </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
@@ -6363,7 +6498,9 @@
       <c r="E135" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F135" s="4"/>
+      <c r="F135" s="4" t="s">
+        <v>447</v>
+      </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
@@ -6396,7 +6533,9 @@
       <c r="E136" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F136" s="4"/>
+      <c r="F136" s="4" t="s">
+        <v>448</v>
+      </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
@@ -6429,7 +6568,9 @@
       <c r="E137" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F137" s="4"/>
+      <c r="F137" s="4" t="s">
+        <v>449</v>
+      </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
@@ -6462,7 +6603,9 @@
       <c r="E138" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F138" s="4"/>
+      <c r="F138" s="4" t="s">
+        <v>450</v>
+      </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
@@ -6495,7 +6638,9 @@
       <c r="E139" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F139" s="4"/>
+      <c r="F139" s="4" t="s">
+        <v>451</v>
+      </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
@@ -6726,7 +6871,9 @@
       <c r="E146" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F146" s="4"/>
+      <c r="F146" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
@@ -6759,7 +6906,9 @@
       <c r="E147" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F147" s="4"/>
+      <c r="F147" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
@@ -6792,7 +6941,9 @@
       <c r="E148" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F148" s="4"/>
+      <c r="F148" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
@@ -6825,7 +6976,9 @@
       <c r="E149" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F149" s="4"/>
+      <c r="F149" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
@@ -6858,7 +7011,9 @@
       <c r="E150" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F150" s="4"/>
+      <c r="F150" s="4" t="s">
+        <v>456</v>
+      </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
@@ -6891,7 +7046,9 @@
       <c r="E151" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F151" s="4"/>
+      <c r="F151" s="4" t="s">
+        <v>457</v>
+      </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
@@ -7122,7 +7279,9 @@
       <c r="E158" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F158" s="4"/>
+      <c r="F158" s="4" t="s">
+        <v>458</v>
+      </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
@@ -7155,7 +7314,9 @@
       <c r="E159" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F159" s="4"/>
+      <c r="F159" s="4" t="s">
+        <v>459</v>
+      </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
@@ -7188,7 +7349,9 @@
       <c r="E160" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F160" s="4"/>
+      <c r="F160" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
@@ -7885,7 +8048,9 @@
       <c r="E181" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F181" s="4"/>
+      <c r="F181" s="4" t="s">
+        <v>428</v>
+      </c>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
@@ -7918,7 +8083,9 @@
       <c r="E182" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F182" s="4"/>
+      <c r="F182" s="4" t="s">
+        <v>462</v>
+      </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
@@ -7951,7 +8118,9 @@
       <c r="E183" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F183" s="4"/>
+      <c r="F183" s="4" t="s">
+        <v>463</v>
+      </c>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
@@ -7984,7 +8153,9 @@
       <c r="E184" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F184" s="4"/>
+      <c r="F184" s="4" t="s">
+        <v>464</v>
+      </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
@@ -8017,7 +8188,9 @@
       <c r="E185" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F185" s="4"/>
+      <c r="F185" s="4" t="s">
+        <v>465</v>
+      </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
@@ -8050,7 +8223,9 @@
       <c r="E186" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F186" s="4"/>
+      <c r="F186" s="4" t="s">
+        <v>466</v>
+      </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
@@ -8083,7 +8258,9 @@
       <c r="E187" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F187" s="4"/>
+      <c r="F187" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Documents\GitHub\ml-knowledge-inject-va\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A0C3C-33BC-4E93-AC8D-893AAF2554E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7C75CA-29F8-4726-B87B-087D3ED6D735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="497">
   <si>
     <t>Paper ID</t>
   </si>
@@ -1485,6 +1485,93 @@
   </si>
   <si>
     <t>10.1109/TVCG.2020.3028894</t>
+  </si>
+  <si>
+    <t>10.1109/VAST50239.2020.00006</t>
+  </si>
+  <si>
+    <t>10.1109/VAST50239.2020.00007</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3012778</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030425</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028975</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3009003</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.2981456</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028976</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.2973258</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030449</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030354</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030342</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3011155</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028957</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030461</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030420</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3028888</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2020.3030418</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934332</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934255</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934806</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934547</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934267</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934629</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934631</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934262</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934659</t>
+  </si>
+  <si>
+    <t>10.1109/VAST47406.2019.8986948</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2921323</t>
   </si>
 </sst>
 </file>
@@ -7419,7 +7506,9 @@
       <c r="E162" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F162" s="4"/>
+      <c r="F162" s="4" t="s">
+        <v>468</v>
+      </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
@@ -7452,7 +7541,9 @@
       <c r="E163" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F163" s="4"/>
+      <c r="F163" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
@@ -7485,7 +7576,9 @@
       <c r="E164" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F164" s="4"/>
+      <c r="F164" s="4" t="s">
+        <v>470</v>
+      </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
@@ -7518,7 +7611,9 @@
       <c r="E165" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F165" s="4"/>
+      <c r="F165" s="4" t="s">
+        <v>471</v>
+      </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
@@ -7551,7 +7646,9 @@
       <c r="E166" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F166" s="4"/>
+      <c r="F166" s="4" t="s">
+        <v>472</v>
+      </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
@@ -7584,7 +7681,9 @@
       <c r="E167" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F167" s="4"/>
+      <c r="F167" s="4" t="s">
+        <v>473</v>
+      </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
@@ -7617,7 +7716,9 @@
       <c r="E168" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F168" s="4"/>
+      <c r="F168" s="4" t="s">
+        <v>474</v>
+      </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
@@ -7650,7 +7751,9 @@
       <c r="E169" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F169" s="4"/>
+      <c r="F169" s="4" t="s">
+        <v>475</v>
+      </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
@@ -7683,7 +7786,9 @@
       <c r="E170" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F170" s="4"/>
+      <c r="F170" s="4" t="s">
+        <v>476</v>
+      </c>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
@@ -7716,7 +7821,9 @@
       <c r="E171" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F171" s="4"/>
+      <c r="F171" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
@@ -7749,7 +7856,9 @@
       <c r="E172" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F172" s="4"/>
+      <c r="F172" s="4" t="s">
+        <v>478</v>
+      </c>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -7782,7 +7891,9 @@
       <c r="E173" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F173" s="4"/>
+      <c r="F173" s="4" t="s">
+        <v>479</v>
+      </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
@@ -7815,7 +7926,9 @@
       <c r="E174" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F174" s="4"/>
+      <c r="F174" s="4" t="s">
+        <v>480</v>
+      </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -7848,7 +7961,9 @@
       <c r="E175" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F175" s="4"/>
+      <c r="F175" s="4" t="s">
+        <v>481</v>
+      </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
@@ -7881,7 +7996,9 @@
       <c r="E176" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F176" s="4"/>
+      <c r="F176" s="4" t="s">
+        <v>482</v>
+      </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
@@ -7914,7 +8031,9 @@
       <c r="E177" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F177" s="4"/>
+      <c r="F177" s="4" t="s">
+        <v>483</v>
+      </c>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
@@ -7947,7 +8066,9 @@
       <c r="E178" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F178" s="4"/>
+      <c r="F178" s="4" t="s">
+        <v>484</v>
+      </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
@@ -7980,7 +8101,9 @@
       <c r="E179" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F179" s="4"/>
+      <c r="F179" s="4" t="s">
+        <v>485</v>
+      </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -8363,7 +8486,9 @@
       <c r="E190" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F190" s="4"/>
+      <c r="F190" s="4" t="s">
+        <v>486</v>
+      </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
@@ -8396,7 +8521,9 @@
       <c r="E191" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F191" s="4"/>
+      <c r="F191" s="4" t="s">
+        <v>487</v>
+      </c>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
@@ -8429,7 +8556,9 @@
       <c r="E192" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F192" s="4"/>
+      <c r="F192" s="4" t="s">
+        <v>488</v>
+      </c>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
@@ -8462,7 +8591,9 @@
       <c r="E193" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F193" s="4"/>
+      <c r="F193" s="4" t="s">
+        <v>489</v>
+      </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
@@ -8495,7 +8626,9 @@
       <c r="E194" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F194" s="4"/>
+      <c r="F194" s="4" t="s">
+        <v>490</v>
+      </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
@@ -8528,7 +8661,9 @@
       <c r="E195" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F195" s="4"/>
+      <c r="F195" s="4" t="s">
+        <v>491</v>
+      </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
@@ -8561,7 +8696,9 @@
       <c r="E196" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F196" s="4"/>
+      <c r="F196" s="4" t="s">
+        <v>492</v>
+      </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
@@ -8594,7 +8731,9 @@
       <c r="E197" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F197" s="4"/>
+      <c r="F197" s="4" t="s">
+        <v>493</v>
+      </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
@@ -8627,7 +8766,9 @@
       <c r="E198" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F198" s="4"/>
+      <c r="F198" s="4" t="s">
+        <v>494</v>
+      </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -8660,7 +8801,9 @@
       <c r="E199" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F199" s="4"/>
+      <c r="F199" s="4" t="s">
+        <v>495</v>
+      </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -8693,7 +8836,9 @@
       <c r="E200" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F200" s="4"/>
+      <c r="F200" s="4" t="s">
+        <v>496</v>
+      </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2653\Documents\GitHub\ml-knowledge-inject-va\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7C75CA-29F8-4726-B87B-087D3ED6D735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD068D1-A653-476A-ACFE-FED43BE36E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="505">
   <si>
     <t>Paper ID</t>
   </si>
@@ -1572,6 +1572,30 @@
   </si>
   <si>
     <t>10.1109/TVCG.2019.2921323</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934399</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934261</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934266</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2019.2934595</t>
+  </si>
+  <si>
+    <t>10.1109/VAST47406.2019.8986923</t>
+  </si>
+  <si>
+    <t>10.1109/VAST47406.2019.8986943</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865138</t>
+  </si>
+  <si>
+    <t>10.1109/TVCG.2018.2865230</t>
   </si>
 </sst>
 </file>
@@ -8871,7 +8895,9 @@
       <c r="E201" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F201" s="4"/>
+      <c r="F201" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
@@ -8904,7 +8930,9 @@
       <c r="E202" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F202" s="4"/>
+      <c r="F202" s="4" t="s">
+        <v>498</v>
+      </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
@@ -8937,7 +8965,9 @@
       <c r="E203" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F203" s="4"/>
+      <c r="F203" s="4" t="s">
+        <v>499</v>
+      </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
@@ -8970,7 +9000,9 @@
       <c r="E204" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F204" s="4"/>
+      <c r="F204" s="4" t="s">
+        <v>500</v>
+      </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
@@ -9003,7 +9035,9 @@
       <c r="E205" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F205" s="4"/>
+      <c r="F205" s="4" t="s">
+        <v>501</v>
+      </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
@@ -9036,7 +9070,9 @@
       <c r="E206" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F206" s="4"/>
+      <c r="F206" s="4" t="s">
+        <v>502</v>
+      </c>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
@@ -9104,7 +9140,9 @@
       <c r="E208" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F208" s="6"/>
+      <c r="F208" s="6" t="s">
+        <v>503</v>
+      </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
@@ -9137,7 +9175,9 @@
       <c r="E209" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F209" s="6"/>
+      <c r="F209" s="6" t="s">
+        <v>504</v>
+      </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
